--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_45.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2423703.59223519</v>
+        <v>2418069.790110335</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11431968.00070023</v>
+        <v>11452050.89429174</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5227602.284138135</v>
+        <v>5225674.076284139</v>
       </c>
     </row>
     <row r="11">
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>340.7338416634806</v>
+        <v>335.9908957873019</v>
       </c>
       <c r="C11" t="n">
-        <v>323.2728917710076</v>
+        <v>318.5299458948289</v>
       </c>
       <c r="D11" t="n">
-        <v>312.683041620683</v>
+        <v>307.9400957445043</v>
       </c>
       <c r="E11" t="n">
-        <v>339.9303700722618</v>
+        <v>335.1874241960831</v>
       </c>
       <c r="F11" t="n">
-        <v>364.8760457417114</v>
+        <v>360.1330998655328</v>
       </c>
       <c r="G11" t="n">
-        <v>373.302737515135</v>
+        <v>368.5597916389564</v>
       </c>
       <c r="H11" t="n">
-        <v>297.4748021157671</v>
+        <v>292.7318562395885</v>
       </c>
       <c r="I11" t="n">
-        <v>168.4758895704059</v>
+        <v>163.7329436942273</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>107.8691179411497</v>
+        <v>103.126172064971</v>
       </c>
       <c r="S11" t="n">
-        <v>167.0200695862453</v>
+        <v>162.2771237100667</v>
       </c>
       <c r="T11" t="n">
-        <v>181.0958495641314</v>
+        <v>176.3529036879527</v>
       </c>
       <c r="U11" t="n">
-        <v>209.3456529078365</v>
+        <v>204.6027070316578</v>
       </c>
       <c r="V11" t="n">
-        <v>285.7522584701349</v>
+        <v>281.0093125939562</v>
       </c>
       <c r="W11" t="n">
-        <v>307.240968717413</v>
+        <v>302.4980228412343</v>
       </c>
       <c r="X11" t="n">
-        <v>327.731100678469</v>
+        <v>322.9881548022904</v>
       </c>
       <c r="Y11" t="n">
-        <v>344.2379386560536</v>
+        <v>339.4949927798749</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>124.5331836498673</v>
+        <v>119.7902377736887</v>
       </c>
       <c r="C12" t="n">
-        <v>130.7084989883157</v>
+        <v>125.9655531121371</v>
       </c>
       <c r="D12" t="n">
-        <v>105.4450655646388</v>
+        <v>100.7021196884601</v>
       </c>
       <c r="E12" t="n">
-        <v>115.6450804554009</v>
+        <v>110.9021345792223</v>
       </c>
       <c r="F12" t="n">
-        <v>103.0692123933839</v>
+        <v>98.32626651720523</v>
       </c>
       <c r="G12" t="n">
-        <v>95.34351716321063</v>
+        <v>90.60057128703198</v>
       </c>
       <c r="H12" t="n">
-        <v>70.23544423649646</v>
+        <v>65.4924983603178</v>
       </c>
       <c r="I12" t="n">
-        <v>47.39663285141508</v>
+        <v>42.65368697523642</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>58.15783415264313</v>
+        <v>53.41488827646447</v>
       </c>
       <c r="S12" t="n">
-        <v>129.6831711038378</v>
+        <v>124.9402252276592</v>
       </c>
       <c r="T12" t="n">
-        <v>158.1647286948216</v>
+        <v>153.421782818643</v>
       </c>
       <c r="U12" t="n">
-        <v>183.9413820809748</v>
+        <v>179.1984362047962</v>
       </c>
       <c r="V12" t="n">
-        <v>190.8005871494253</v>
+        <v>186.0576412732466</v>
       </c>
       <c r="W12" t="n">
-        <v>209.6949831609196</v>
+        <v>204.952037284741</v>
       </c>
       <c r="X12" t="n">
-        <v>163.7729852034775</v>
+        <v>159.0300393272988</v>
       </c>
       <c r="Y12" t="n">
-        <v>163.6826957773044</v>
+        <v>158.9397499011257</v>
       </c>
     </row>
     <row r="13">
@@ -23373,31 +23373,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>137.8319801819373</v>
+        <v>133.0890343057586</v>
       </c>
       <c r="C13" t="n">
-        <v>125.2468210986278</v>
+        <v>120.5038752224492</v>
       </c>
       <c r="D13" t="n">
-        <v>106.6154730182124</v>
+        <v>101.8725271420337</v>
       </c>
       <c r="E13" t="n">
-        <v>104.4339626465692</v>
+        <v>99.69101677039052</v>
       </c>
       <c r="F13" t="n">
-        <v>103.4210480229312</v>
+        <v>98.67810214675259</v>
       </c>
       <c r="G13" t="n">
-        <v>125.9909793584588</v>
+        <v>121.2480334822801</v>
       </c>
       <c r="H13" t="n">
-        <v>120.2271725074396</v>
+        <v>115.4842266312609</v>
       </c>
       <c r="I13" t="n">
-        <v>113.4504749272583</v>
+        <v>108.7075290510796</v>
       </c>
       <c r="J13" t="n">
-        <v>51.35918011667277</v>
+        <v>46.61623424049412</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.16204325169439</v>
+        <v>39.41909737551573</v>
       </c>
       <c r="R13" t="n">
-        <v>135.2933913771695</v>
+        <v>130.5504455009908</v>
       </c>
       <c r="S13" t="n">
-        <v>182.0165980369723</v>
+        <v>177.2736521607936</v>
       </c>
       <c r="T13" t="n">
-        <v>185.9455894282815</v>
+        <v>181.2026435521028</v>
       </c>
       <c r="U13" t="n">
-        <v>244.3190293564909</v>
+        <v>239.5760834803122</v>
       </c>
       <c r="V13" t="n">
-        <v>210.137643323828</v>
+        <v>205.3946974476493</v>
       </c>
       <c r="W13" t="n">
-        <v>244.522998336591</v>
+        <v>239.7800524604123</v>
       </c>
       <c r="X13" t="n">
-        <v>183.7096553890372</v>
+        <v>178.9667095128585</v>
       </c>
       <c r="Y13" t="n">
-        <v>176.5846533520948</v>
+        <v>171.8417074759161</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,28 +23610,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,28 +23847,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,28 +24084,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,28 +24321,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>295.7338416634806</v>
+        <v>296.5717984117862</v>
       </c>
       <c r="C26" t="n">
-        <v>278.2728917710076</v>
+        <v>279.1108485193132</v>
       </c>
       <c r="D26" t="n">
-        <v>267.683041620683</v>
+        <v>268.5209983689886</v>
       </c>
       <c r="E26" t="n">
-        <v>294.9303700722618</v>
+        <v>295.7683268205674</v>
       </c>
       <c r="F26" t="n">
-        <v>319.8760457417114</v>
+        <v>320.714002490017</v>
       </c>
       <c r="G26" t="n">
-        <v>328.302737515135</v>
+        <v>329.1406942634407</v>
       </c>
       <c r="H26" t="n">
-        <v>252.4748021157671</v>
+        <v>253.3127588640728</v>
       </c>
       <c r="I26" t="n">
-        <v>123.4758895704059</v>
+        <v>124.3138463187115</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>62.86911794114968</v>
+        <v>63.70707468945531</v>
       </c>
       <c r="S26" t="n">
-        <v>122.0200695862453</v>
+        <v>122.858026334551</v>
       </c>
       <c r="T26" t="n">
-        <v>136.0958495641314</v>
+        <v>136.933806312437</v>
       </c>
       <c r="U26" t="n">
-        <v>164.3456529078365</v>
+        <v>165.1836096561421</v>
       </c>
       <c r="V26" t="n">
-        <v>240.7522584701349</v>
+        <v>241.5902152184405</v>
       </c>
       <c r="W26" t="n">
-        <v>262.240968717413</v>
+        <v>263.0789254657186</v>
       </c>
       <c r="X26" t="n">
-        <v>282.731100678469</v>
+        <v>283.5690574267746</v>
       </c>
       <c r="Y26" t="n">
-        <v>299.2379386560536</v>
+        <v>300.0758954043592</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79.53318364986734</v>
+        <v>80.37114039817297</v>
       </c>
       <c r="C27" t="n">
-        <v>85.70849898831574</v>
+        <v>86.54645573662137</v>
       </c>
       <c r="D27" t="n">
-        <v>60.44506556463875</v>
+        <v>61.28302231294438</v>
       </c>
       <c r="E27" t="n">
-        <v>70.64508045540094</v>
+        <v>71.48303720370657</v>
       </c>
       <c r="F27" t="n">
-        <v>58.06921239338388</v>
+        <v>58.90716914168951</v>
       </c>
       <c r="G27" t="n">
-        <v>50.34351716321063</v>
+        <v>51.18147391151626</v>
       </c>
       <c r="H27" t="n">
-        <v>25.23544423649646</v>
+        <v>26.07340098480209</v>
       </c>
       <c r="I27" t="n">
-        <v>2.396632851415077</v>
+        <v>3.234589599720707</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>13.15783415264313</v>
+        <v>13.99579090094876</v>
       </c>
       <c r="S27" t="n">
-        <v>84.68317110383782</v>
+        <v>85.52112785214345</v>
       </c>
       <c r="T27" t="n">
-        <v>113.1647286948216</v>
+        <v>114.0026854431272</v>
       </c>
       <c r="U27" t="n">
-        <v>138.9413820809748</v>
+        <v>139.7793388292804</v>
       </c>
       <c r="V27" t="n">
-        <v>145.8005871494253</v>
+        <v>146.6385438977309</v>
       </c>
       <c r="W27" t="n">
-        <v>164.6949831609196</v>
+        <v>165.5329399092252</v>
       </c>
       <c r="X27" t="n">
-        <v>118.7729852034775</v>
+        <v>119.6109419517831</v>
       </c>
       <c r="Y27" t="n">
-        <v>118.6826957773044</v>
+        <v>119.52065252561</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>92.8319801819373</v>
+        <v>93.66993693024293</v>
       </c>
       <c r="C28" t="n">
-        <v>80.24682109862783</v>
+        <v>81.08477784693346</v>
       </c>
       <c r="D28" t="n">
-        <v>61.61547301821236</v>
+        <v>62.45342976651798</v>
       </c>
       <c r="E28" t="n">
-        <v>59.43396264656917</v>
+        <v>60.2719193948748</v>
       </c>
       <c r="F28" t="n">
-        <v>58.42104802293125</v>
+        <v>59.25900477123687</v>
       </c>
       <c r="G28" t="n">
-        <v>80.99097935845876</v>
+        <v>81.82893610676439</v>
       </c>
       <c r="H28" t="n">
-        <v>75.22717250743958</v>
+        <v>76.06512925574521</v>
       </c>
       <c r="I28" t="n">
-        <v>68.45047492725828</v>
+        <v>69.28843167556391</v>
       </c>
       <c r="J28" t="n">
-        <v>6.359180116672775</v>
+        <v>7.197136864978404</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>90.29339137716948</v>
+        <v>91.13134812547511</v>
       </c>
       <c r="S28" t="n">
-        <v>137.0165980369723</v>
+        <v>137.8545547852779</v>
       </c>
       <c r="T28" t="n">
-        <v>140.9455894282815</v>
+        <v>141.7835461765871</v>
       </c>
       <c r="U28" t="n">
-        <v>199.3190293564909</v>
+        <v>200.1569861047965</v>
       </c>
       <c r="V28" t="n">
-        <v>165.137643323828</v>
+        <v>165.9756000721336</v>
       </c>
       <c r="W28" t="n">
-        <v>199.522998336591</v>
+        <v>200.3609550848966</v>
       </c>
       <c r="X28" t="n">
-        <v>138.7096553890372</v>
+        <v>139.5476121373428</v>
       </c>
       <c r="Y28" t="n">
-        <v>131.5846533520948</v>
+        <v>132.4226101004004</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>249.7338416634806</v>
+        <v>249.8288525356076</v>
       </c>
       <c r="C29" t="n">
-        <v>232.2728917710076</v>
+        <v>232.3679026431345</v>
       </c>
       <c r="D29" t="n">
-        <v>221.683041620683</v>
+        <v>221.7780524928099</v>
       </c>
       <c r="E29" t="n">
-        <v>248.9303700722618</v>
+        <v>249.0253809443888</v>
       </c>
       <c r="F29" t="n">
-        <v>273.8760457417114</v>
+        <v>273.9710566138384</v>
       </c>
       <c r="G29" t="n">
-        <v>282.302737515135</v>
+        <v>282.397748387262</v>
       </c>
       <c r="H29" t="n">
-        <v>206.4748021157671</v>
+        <v>206.5698129878941</v>
       </c>
       <c r="I29" t="n">
-        <v>77.47588957040591</v>
+        <v>77.57090044253289</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>16.86911794114968</v>
+        <v>16.96412881327666</v>
       </c>
       <c r="S29" t="n">
-        <v>76.02006958624534</v>
+        <v>76.11508045837232</v>
       </c>
       <c r="T29" t="n">
-        <v>90.09584956413136</v>
+        <v>90.19086043625833</v>
       </c>
       <c r="U29" t="n">
-        <v>118.3456529078365</v>
+        <v>118.4406637799635</v>
       </c>
       <c r="V29" t="n">
-        <v>194.7522584701349</v>
+        <v>194.8472693422619</v>
       </c>
       <c r="W29" t="n">
-        <v>216.240968717413</v>
+        <v>216.33597958954</v>
       </c>
       <c r="X29" t="n">
-        <v>236.731100678469</v>
+        <v>236.826111550596</v>
       </c>
       <c r="Y29" t="n">
-        <v>253.2379386560536</v>
+        <v>253.3329495281806</v>
       </c>
     </row>
     <row r="30">
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.53318364986734</v>
+        <v>33.62819452199432</v>
       </c>
       <c r="C30" t="n">
-        <v>39.70849898831574</v>
+        <v>39.80350986044272</v>
       </c>
       <c r="D30" t="n">
-        <v>14.44506556463875</v>
+        <v>14.54007643676573</v>
       </c>
       <c r="E30" t="n">
-        <v>24.64508045540094</v>
+        <v>24.74009132752792</v>
       </c>
       <c r="F30" t="n">
-        <v>12.06921239338388</v>
+        <v>12.16422326551086</v>
       </c>
       <c r="G30" t="n">
-        <v>4.343517163210635</v>
+        <v>4.438528035337612</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>38.68317110383782</v>
+        <v>38.7781819759648</v>
       </c>
       <c r="T30" t="n">
-        <v>67.1647286948216</v>
+        <v>67.25973956694858</v>
       </c>
       <c r="U30" t="n">
-        <v>92.94138208097482</v>
+        <v>93.0363929531018</v>
       </c>
       <c r="V30" t="n">
-        <v>99.80058714942527</v>
+        <v>99.89559802155225</v>
       </c>
       <c r="W30" t="n">
-        <v>118.6949831609196</v>
+        <v>118.7899940330466</v>
       </c>
       <c r="X30" t="n">
-        <v>72.77298520347748</v>
+        <v>72.86799607560445</v>
       </c>
       <c r="Y30" t="n">
-        <v>72.68269577730436</v>
+        <v>72.77770664943134</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46.8319801819373</v>
+        <v>46.92699105406427</v>
       </c>
       <c r="C31" t="n">
-        <v>34.24682109862783</v>
+        <v>34.34183197075481</v>
       </c>
       <c r="D31" t="n">
-        <v>15.61547301821236</v>
+        <v>15.71048389033933</v>
       </c>
       <c r="E31" t="n">
-        <v>13.43396264656917</v>
+        <v>13.52897351869615</v>
       </c>
       <c r="F31" t="n">
-        <v>12.42104802293125</v>
+        <v>12.51605889505822</v>
       </c>
       <c r="G31" t="n">
-        <v>34.99097935845876</v>
+        <v>35.08599023058574</v>
       </c>
       <c r="H31" t="n">
-        <v>29.22717250743958</v>
+        <v>29.32218337956655</v>
       </c>
       <c r="I31" t="n">
-        <v>22.45047492725828</v>
+        <v>22.54548579938526</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>44.29339137716948</v>
+        <v>44.38840224929646</v>
       </c>
       <c r="S31" t="n">
-        <v>91.01659803697225</v>
+        <v>91.11160890909923</v>
       </c>
       <c r="T31" t="n">
-        <v>94.94558942828149</v>
+        <v>95.04060030040847</v>
       </c>
       <c r="U31" t="n">
-        <v>153.3190293564909</v>
+        <v>153.4140402286179</v>
       </c>
       <c r="V31" t="n">
-        <v>119.137643323828</v>
+        <v>119.232654195955</v>
       </c>
       <c r="W31" t="n">
-        <v>153.522998336591</v>
+        <v>153.618009208718</v>
       </c>
       <c r="X31" t="n">
-        <v>92.70965538903715</v>
+        <v>92.80466626116413</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.58465335209479</v>
+        <v>85.67966422422177</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>249.7338416634806</v>
+        <v>249.8288525356076</v>
       </c>
       <c r="C32" t="n">
-        <v>232.2728917710076</v>
+        <v>232.3679026431345</v>
       </c>
       <c r="D32" t="n">
-        <v>221.683041620683</v>
+        <v>221.7780524928099</v>
       </c>
       <c r="E32" t="n">
-        <v>248.9303700722618</v>
+        <v>249.0253809443888</v>
       </c>
       <c r="F32" t="n">
-        <v>273.8760457417114</v>
+        <v>273.9710566138384</v>
       </c>
       <c r="G32" t="n">
-        <v>282.302737515135</v>
+        <v>282.397748387262</v>
       </c>
       <c r="H32" t="n">
-        <v>206.4748021157671</v>
+        <v>206.5698129878941</v>
       </c>
       <c r="I32" t="n">
-        <v>77.47588957040591</v>
+        <v>77.57090044253289</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>16.86911794114968</v>
+        <v>16.96412881327666</v>
       </c>
       <c r="S32" t="n">
-        <v>76.02006958624534</v>
+        <v>76.11508045837232</v>
       </c>
       <c r="T32" t="n">
-        <v>90.09584956413136</v>
+        <v>90.19086043625833</v>
       </c>
       <c r="U32" t="n">
-        <v>118.3456529078365</v>
+        <v>118.4406637799635</v>
       </c>
       <c r="V32" t="n">
-        <v>194.7522584701349</v>
+        <v>194.8472693422619</v>
       </c>
       <c r="W32" t="n">
-        <v>216.240968717413</v>
+        <v>216.33597958954</v>
       </c>
       <c r="X32" t="n">
-        <v>236.731100678469</v>
+        <v>236.826111550596</v>
       </c>
       <c r="Y32" t="n">
-        <v>253.2379386560536</v>
+        <v>253.3329495281806</v>
       </c>
     </row>
     <row r="33">
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>33.53318364986734</v>
+        <v>33.62819452199432</v>
       </c>
       <c r="C33" t="n">
-        <v>39.70849898831574</v>
+        <v>39.80350986044272</v>
       </c>
       <c r="D33" t="n">
-        <v>14.44506556463875</v>
+        <v>14.54007643676573</v>
       </c>
       <c r="E33" t="n">
-        <v>24.64508045540094</v>
+        <v>24.74009132752792</v>
       </c>
       <c r="F33" t="n">
-        <v>12.06921239338388</v>
+        <v>12.16422326551086</v>
       </c>
       <c r="G33" t="n">
-        <v>4.343517163210635</v>
+        <v>4.438528035337612</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>38.68317110383782</v>
+        <v>38.7781819759648</v>
       </c>
       <c r="T33" t="n">
-        <v>67.1647286948216</v>
+        <v>67.25973956694858</v>
       </c>
       <c r="U33" t="n">
-        <v>92.94138208097482</v>
+        <v>93.0363929531018</v>
       </c>
       <c r="V33" t="n">
-        <v>99.80058714942527</v>
+        <v>99.89559802155225</v>
       </c>
       <c r="W33" t="n">
-        <v>118.6949831609196</v>
+        <v>118.7899940330466</v>
       </c>
       <c r="X33" t="n">
-        <v>72.77298520347748</v>
+        <v>72.86799607560445</v>
       </c>
       <c r="Y33" t="n">
-        <v>72.68269577730436</v>
+        <v>72.77770664943134</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>46.8319801819373</v>
+        <v>46.92699105406427</v>
       </c>
       <c r="C34" t="n">
-        <v>34.24682109862783</v>
+        <v>34.34183197075481</v>
       </c>
       <c r="D34" t="n">
-        <v>15.61547301821236</v>
+        <v>15.71048389033933</v>
       </c>
       <c r="E34" t="n">
-        <v>13.43396264656917</v>
+        <v>13.52897351869615</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42104802293125</v>
+        <v>12.51605889505822</v>
       </c>
       <c r="G34" t="n">
-        <v>34.99097935845876</v>
+        <v>35.08599023058574</v>
       </c>
       <c r="H34" t="n">
-        <v>29.22717250743958</v>
+        <v>29.32218337956655</v>
       </c>
       <c r="I34" t="n">
-        <v>22.45047492725828</v>
+        <v>22.54548579938526</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>44.29339137716948</v>
+        <v>44.38840224929646</v>
       </c>
       <c r="S34" t="n">
-        <v>91.01659803697225</v>
+        <v>91.11160890909923</v>
       </c>
       <c r="T34" t="n">
-        <v>94.94558942828149</v>
+        <v>95.04060030040847</v>
       </c>
       <c r="U34" t="n">
-        <v>153.3190293564909</v>
+        <v>153.4140402286179</v>
       </c>
       <c r="V34" t="n">
-        <v>119.137643323828</v>
+        <v>119.232654195955</v>
       </c>
       <c r="W34" t="n">
-        <v>153.522998336591</v>
+        <v>153.618009208718</v>
       </c>
       <c r="X34" t="n">
-        <v>92.70965538903715</v>
+        <v>92.80466626116413</v>
       </c>
       <c r="Y34" t="n">
-        <v>85.58465335209479</v>
+        <v>85.67966422422177</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>249.7338416634806</v>
+        <v>249.8288525356076</v>
       </c>
       <c r="C35" t="n">
-        <v>232.2728917710076</v>
+        <v>232.3679026431345</v>
       </c>
       <c r="D35" t="n">
-        <v>221.683041620683</v>
+        <v>221.7780524928099</v>
       </c>
       <c r="E35" t="n">
-        <v>248.9303700722618</v>
+        <v>249.0253809443888</v>
       </c>
       <c r="F35" t="n">
-        <v>273.8760457417114</v>
+        <v>273.9710566138384</v>
       </c>
       <c r="G35" t="n">
-        <v>282.302737515135</v>
+        <v>282.397748387262</v>
       </c>
       <c r="H35" t="n">
-        <v>206.4748021157671</v>
+        <v>206.5698129878941</v>
       </c>
       <c r="I35" t="n">
-        <v>77.47588957040591</v>
+        <v>77.57090044253289</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>16.86911794114968</v>
+        <v>16.96412881327666</v>
       </c>
       <c r="S35" t="n">
-        <v>76.02006958624534</v>
+        <v>76.11508045837232</v>
       </c>
       <c r="T35" t="n">
-        <v>90.09584956413136</v>
+        <v>90.19086043625833</v>
       </c>
       <c r="U35" t="n">
-        <v>118.3456529078365</v>
+        <v>118.4406637799635</v>
       </c>
       <c r="V35" t="n">
-        <v>194.7522584701349</v>
+        <v>194.8472693422619</v>
       </c>
       <c r="W35" t="n">
-        <v>216.240968717413</v>
+        <v>216.33597958954</v>
       </c>
       <c r="X35" t="n">
-        <v>236.731100678469</v>
+        <v>236.826111550596</v>
       </c>
       <c r="Y35" t="n">
-        <v>253.2379386560536</v>
+        <v>253.3329495281806</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>33.53318364986734</v>
+        <v>33.62819452199432</v>
       </c>
       <c r="C36" t="n">
-        <v>39.70849898831574</v>
+        <v>39.80350986044272</v>
       </c>
       <c r="D36" t="n">
-        <v>14.44506556463875</v>
+        <v>14.54007643676573</v>
       </c>
       <c r="E36" t="n">
-        <v>24.64508045540094</v>
+        <v>24.74009132752792</v>
       </c>
       <c r="F36" t="n">
-        <v>12.06921239338388</v>
+        <v>12.16422326551086</v>
       </c>
       <c r="G36" t="n">
-        <v>4.343517163210635</v>
+        <v>4.438528035337612</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>38.68317110383782</v>
+        <v>38.7781819759648</v>
       </c>
       <c r="T36" t="n">
-        <v>67.1647286948216</v>
+        <v>67.25973956694858</v>
       </c>
       <c r="U36" t="n">
-        <v>92.94138208097482</v>
+        <v>93.0363929531018</v>
       </c>
       <c r="V36" t="n">
-        <v>99.80058714942527</v>
+        <v>99.89559802155225</v>
       </c>
       <c r="W36" t="n">
-        <v>118.6949831609196</v>
+        <v>118.7899940330466</v>
       </c>
       <c r="X36" t="n">
-        <v>72.77298520347748</v>
+        <v>72.86799607560445</v>
       </c>
       <c r="Y36" t="n">
-        <v>72.68269577730436</v>
+        <v>72.77770664943134</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>46.8319801819373</v>
+        <v>46.92699105406427</v>
       </c>
       <c r="C37" t="n">
-        <v>34.24682109862783</v>
+        <v>34.34183197075481</v>
       </c>
       <c r="D37" t="n">
-        <v>15.61547301821236</v>
+        <v>15.71048389033933</v>
       </c>
       <c r="E37" t="n">
-        <v>13.43396264656917</v>
+        <v>13.52897351869615</v>
       </c>
       <c r="F37" t="n">
-        <v>12.42104802293125</v>
+        <v>12.51605889505822</v>
       </c>
       <c r="G37" t="n">
-        <v>34.99097935845876</v>
+        <v>35.08599023058574</v>
       </c>
       <c r="H37" t="n">
-        <v>29.22717250743958</v>
+        <v>29.32218337956655</v>
       </c>
       <c r="I37" t="n">
-        <v>22.45047492725828</v>
+        <v>22.54548579938526</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>44.29339137716948</v>
+        <v>44.38840224929646</v>
       </c>
       <c r="S37" t="n">
-        <v>91.01659803697225</v>
+        <v>91.11160890909923</v>
       </c>
       <c r="T37" t="n">
-        <v>94.94558942828149</v>
+        <v>95.04060030040847</v>
       </c>
       <c r="U37" t="n">
-        <v>153.3190293564909</v>
+        <v>153.4140402286179</v>
       </c>
       <c r="V37" t="n">
-        <v>119.137643323828</v>
+        <v>119.232654195955</v>
       </c>
       <c r="W37" t="n">
-        <v>153.522998336591</v>
+        <v>153.618009208718</v>
       </c>
       <c r="X37" t="n">
-        <v>92.70965538903715</v>
+        <v>92.80466626116413</v>
       </c>
       <c r="Y37" t="n">
-        <v>85.58465335209479</v>
+        <v>85.67966422422177</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>249.7338416634806</v>
+        <v>249.8288525356076</v>
       </c>
       <c r="C38" t="n">
-        <v>232.2728917710076</v>
+        <v>232.3679026431345</v>
       </c>
       <c r="D38" t="n">
-        <v>221.683041620683</v>
+        <v>221.7780524928099</v>
       </c>
       <c r="E38" t="n">
-        <v>248.9303700722618</v>
+        <v>249.0253809443888</v>
       </c>
       <c r="F38" t="n">
-        <v>273.8760457417114</v>
+        <v>273.9710566138384</v>
       </c>
       <c r="G38" t="n">
-        <v>282.302737515135</v>
+        <v>282.397748387262</v>
       </c>
       <c r="H38" t="n">
-        <v>206.4748021157671</v>
+        <v>206.5698129878941</v>
       </c>
       <c r="I38" t="n">
-        <v>77.47588957040591</v>
+        <v>77.57090044253289</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>16.86911794114968</v>
+        <v>16.96412881327666</v>
       </c>
       <c r="S38" t="n">
-        <v>76.02006958624534</v>
+        <v>76.11508045837232</v>
       </c>
       <c r="T38" t="n">
-        <v>90.09584956413136</v>
+        <v>90.19086043625833</v>
       </c>
       <c r="U38" t="n">
-        <v>118.3456529078365</v>
+        <v>118.4406637799635</v>
       </c>
       <c r="V38" t="n">
-        <v>194.7522584701349</v>
+        <v>194.8472693422619</v>
       </c>
       <c r="W38" t="n">
-        <v>216.240968717413</v>
+        <v>216.33597958954</v>
       </c>
       <c r="X38" t="n">
-        <v>236.731100678469</v>
+        <v>236.826111550596</v>
       </c>
       <c r="Y38" t="n">
-        <v>253.2379386560536</v>
+        <v>253.3329495281806</v>
       </c>
     </row>
     <row r="39">
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>33.53318364986734</v>
+        <v>33.62819452199432</v>
       </c>
       <c r="C39" t="n">
-        <v>39.70849898831574</v>
+        <v>39.80350986044272</v>
       </c>
       <c r="D39" t="n">
-        <v>14.44506556463875</v>
+        <v>14.54007643676573</v>
       </c>
       <c r="E39" t="n">
-        <v>24.64508045540094</v>
+        <v>24.74009132752792</v>
       </c>
       <c r="F39" t="n">
-        <v>12.06921239338388</v>
+        <v>12.16422326551086</v>
       </c>
       <c r="G39" t="n">
-        <v>4.343517163210635</v>
+        <v>4.438528035337612</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>38.68317110383782</v>
+        <v>38.7781819759648</v>
       </c>
       <c r="T39" t="n">
-        <v>67.1647286948216</v>
+        <v>67.25973956694858</v>
       </c>
       <c r="U39" t="n">
-        <v>92.94138208097482</v>
+        <v>93.0363929531018</v>
       </c>
       <c r="V39" t="n">
-        <v>99.80058714942527</v>
+        <v>99.89559802155225</v>
       </c>
       <c r="W39" t="n">
-        <v>118.6949831609196</v>
+        <v>118.7899940330466</v>
       </c>
       <c r="X39" t="n">
-        <v>72.77298520347748</v>
+        <v>72.86799607560445</v>
       </c>
       <c r="Y39" t="n">
-        <v>72.68269577730436</v>
+        <v>72.77770664943134</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>46.8319801819373</v>
+        <v>46.92699105406427</v>
       </c>
       <c r="C40" t="n">
-        <v>34.24682109862783</v>
+        <v>34.34183197075481</v>
       </c>
       <c r="D40" t="n">
-        <v>15.61547301821236</v>
+        <v>15.71048389033933</v>
       </c>
       <c r="E40" t="n">
-        <v>13.43396264656917</v>
+        <v>13.52897351869615</v>
       </c>
       <c r="F40" t="n">
-        <v>12.42104802293125</v>
+        <v>12.51605889505822</v>
       </c>
       <c r="G40" t="n">
-        <v>34.99097935845876</v>
+        <v>35.08599023058574</v>
       </c>
       <c r="H40" t="n">
-        <v>29.22717250743958</v>
+        <v>29.32218337956655</v>
       </c>
       <c r="I40" t="n">
-        <v>22.45047492725828</v>
+        <v>22.54548579938526</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>44.29339137716948</v>
+        <v>44.38840224929646</v>
       </c>
       <c r="S40" t="n">
-        <v>91.01659803697225</v>
+        <v>91.11160890909923</v>
       </c>
       <c r="T40" t="n">
-        <v>94.94558942828149</v>
+        <v>95.04060030040847</v>
       </c>
       <c r="U40" t="n">
-        <v>153.3190293564909</v>
+        <v>153.4140402286179</v>
       </c>
       <c r="V40" t="n">
-        <v>119.137643323828</v>
+        <v>119.232654195955</v>
       </c>
       <c r="W40" t="n">
-        <v>153.522998336591</v>
+        <v>153.618009208718</v>
       </c>
       <c r="X40" t="n">
-        <v>92.70965538903715</v>
+        <v>92.80466626116413</v>
       </c>
       <c r="Y40" t="n">
-        <v>85.58465335209479</v>
+        <v>85.67966422422177</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>284.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C41" t="n">
-        <v>267.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D41" t="n">
-        <v>256.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E41" t="n">
-        <v>283.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F41" t="n">
-        <v>308.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G41" t="n">
-        <v>317.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H41" t="n">
-        <v>241.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I41" t="n">
-        <v>112.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>51.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S41" t="n">
-        <v>111.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T41" t="n">
-        <v>125.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U41" t="n">
-        <v>153.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V41" t="n">
-        <v>229.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W41" t="n">
-        <v>251.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X41" t="n">
-        <v>271.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y41" t="n">
-        <v>288.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="42">
@@ -25664,25 +25664,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C42" t="n">
-        <v>74.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D42" t="n">
-        <v>49.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E42" t="n">
-        <v>59.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F42" t="n">
-        <v>47.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G42" t="n">
-        <v>39.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H42" t="n">
-        <v>14.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25712,28 +25712,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S42" t="n">
-        <v>73.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T42" t="n">
-        <v>102.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U42" t="n">
-        <v>127.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V42" t="n">
-        <v>134.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W42" t="n">
-        <v>153.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X42" t="n">
-        <v>107.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y42" t="n">
-        <v>107.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>81.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C43" t="n">
-        <v>69.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D43" t="n">
-        <v>50.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E43" t="n">
-        <v>48.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F43" t="n">
-        <v>47.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G43" t="n">
-        <v>69.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H43" t="n">
-        <v>64.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I43" t="n">
-        <v>57.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>79.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S43" t="n">
-        <v>126.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T43" t="n">
-        <v>129.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U43" t="n">
-        <v>188.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V43" t="n">
-        <v>154.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W43" t="n">
-        <v>188.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X43" t="n">
-        <v>127.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y43" t="n">
-        <v>120.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>316708.5660887755</v>
+        <v>323775.5554442815</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>393939.3952098634</v>
+        <v>393020.7799071138</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>393939.3952098634</v>
+        <v>393020.7799071138</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>393939.3952098634</v>
+        <v>393020.7799071138</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>393939.3952098634</v>
+        <v>393020.7799071138</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>383745.9967375508</v>
+        <v>382510.0105337999</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>448425.3170871757</v>
+        <v>448294.1545782044</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>448425.3170871757</v>
+        <v>448294.1545782044</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>448425.3170871757</v>
+        <v>448294.1545782044</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>448425.3170871757</v>
+        <v>448294.1545782044</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>399673.3952098635</v>
+        <v>393020.7799071138</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>921685.881056668</v>
+        <v>921685.8810566685</v>
       </c>
       <c r="C2" t="n">
-        <v>921685.8810566681</v>
+        <v>921685.8810566682</v>
       </c>
       <c r="D2" t="n">
-        <v>921685.881056668</v>
+        <v>921685.8810566682</v>
       </c>
       <c r="E2" t="n">
-        <v>357210.7560075316</v>
+        <v>369931.3368474425</v>
       </c>
       <c r="F2" t="n">
-        <v>496226.24842549</v>
+        <v>494572.740880541</v>
       </c>
       <c r="G2" t="n">
-        <v>496226.24842549</v>
+        <v>494572.7408805409</v>
       </c>
       <c r="H2" t="n">
-        <v>496226.24842549</v>
+        <v>494572.7408805409</v>
       </c>
       <c r="I2" t="n">
-        <v>496226.24842549</v>
+        <v>494572.7408805409</v>
       </c>
       <c r="J2" t="n">
-        <v>477878.1311753273</v>
+        <v>475653.356008576</v>
       </c>
       <c r="K2" t="n">
-        <v>594300.9078046521</v>
+        <v>594064.815288504</v>
       </c>
       <c r="L2" t="n">
-        <v>594300.907804652</v>
+        <v>594064.815288504</v>
       </c>
       <c r="M2" t="n">
-        <v>594300.907804652</v>
+        <v>594064.8152885041</v>
       </c>
       <c r="N2" t="n">
-        <v>594300.9078046521</v>
+        <v>594064.815288504</v>
       </c>
       <c r="O2" t="n">
-        <v>506547.4484254901</v>
+        <v>494572.7408805409</v>
       </c>
       <c r="P2" t="n">
         <v>241891.6624457544</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>33600</v>
+        <v>37394.35670094292</v>
       </c>
       <c r="F3" t="n">
-        <v>41600</v>
+        <v>37292.98739239529</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>28000</v>
+        <v>31636.6472089602</v>
       </c>
       <c r="K3" t="n">
-        <v>78400</v>
+        <v>74687.34409333822</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="C4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.333129713</v>
       </c>
       <c r="D4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="E4" t="n">
-        <v>176765.1165640836</v>
+        <v>183912.4863477087</v>
       </c>
       <c r="F4" t="n">
-        <v>247294.4197339227</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="G4" t="n">
-        <v>247294.4197339226</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="H4" t="n">
-        <v>247294.4197339227</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="I4" t="n">
-        <v>247294.4197339226</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="J4" t="n">
-        <v>237985.5297560938</v>
+        <v>237550.395414165</v>
       </c>
       <c r="K4" t="n">
-        <v>297052.4521972025</v>
+        <v>297626.2730381341</v>
       </c>
       <c r="L4" t="n">
-        <v>297052.4521972025</v>
+        <v>297626.2730381341</v>
       </c>
       <c r="M4" t="n">
-        <v>297052.4521972025</v>
+        <v>297626.2730381341</v>
       </c>
       <c r="N4" t="n">
-        <v>297052.4521972025</v>
+        <v>297626.2730381341</v>
       </c>
       <c r="O4" t="n">
-        <v>252530.8651920154</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="P4" t="n">
-        <v>118258.146084591</v>
+        <v>118951.7481121942</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3530.898</v>
+        <v>3929.632716864464</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>7314.003000000001</v>
+        <v>7243.556814126694</v>
       </c>
       <c r="K5" t="n">
-        <v>11181.177</v>
+        <v>11173.18953099116</v>
       </c>
       <c r="L5" t="n">
-        <v>11181.177</v>
+        <v>11173.18953099116</v>
       </c>
       <c r="M5" t="n">
-        <v>11181.177</v>
+        <v>11173.18953099116</v>
       </c>
       <c r="N5" t="n">
-        <v>11181.177</v>
+        <v>11173.18953099116</v>
       </c>
       <c r="O5" t="n">
-        <v>8238.762000000001</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>424907.5499545583</v>
+        <v>424213.9479269556</v>
       </c>
       <c r="C6" t="n">
-        <v>424907.5499545584</v>
+        <v>424213.9479269553</v>
       </c>
       <c r="D6" t="n">
-        <v>424907.5499545583</v>
+        <v>424213.9479269554</v>
       </c>
       <c r="E6" t="n">
-        <v>143314.741443448</v>
+        <v>144694.8610819264</v>
       </c>
       <c r="F6" t="n">
-        <v>199429.3426915673</v>
+        <v>202282.0234052674</v>
       </c>
       <c r="G6" t="n">
-        <v>241029.3426915674</v>
+        <v>239575.0107976626</v>
       </c>
       <c r="H6" t="n">
-        <v>241029.3426915674</v>
+        <v>239575.0107976627</v>
       </c>
       <c r="I6" t="n">
-        <v>241029.3426915674</v>
+        <v>239575.0107976626</v>
       </c>
       <c r="J6" t="n">
-        <v>204578.5984192335</v>
+        <v>199222.7565713241</v>
       </c>
       <c r="K6" t="n">
-        <v>207667.2786074496</v>
+        <v>210578.0086260405</v>
       </c>
       <c r="L6" t="n">
-        <v>286067.2786074495</v>
+        <v>285265.3527193788</v>
       </c>
       <c r="M6" t="n">
-        <v>286067.2786074495</v>
+        <v>285265.3527193789</v>
       </c>
       <c r="N6" t="n">
-        <v>286067.2786074496</v>
+        <v>285265.3527193788</v>
       </c>
       <c r="O6" t="n">
-        <v>245777.8212334748</v>
+        <v>239575.0107976627</v>
       </c>
       <c r="P6" t="n">
-        <v>123633.5163611633</v>
+        <v>122939.9143335602</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="K2" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="L2" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="M2" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="N2" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="O2" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>46.61623424049412</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>35</v>
+        <v>39.54580901120025</v>
       </c>
       <c r="K2" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26907,13 +26907,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26931,10 +26931,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="K2" t="n">
-        <v>52</v>
+        <v>46.61623424049412</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>39.54580901120025</v>
       </c>
       <c r="P2" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="3">
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="H11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="I11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="S11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="U11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="V11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="W11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="X11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="Y11" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="G12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="H12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="I12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="S12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="T12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="U12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="V12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="W12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="X12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="Y12" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
     </row>
     <row r="13">
@@ -28170,31 +28170,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="G13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="H13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="I13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="J13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="K13" t="n">
         <v>22.26949182588285</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="R13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="S13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="T13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="U13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="V13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="W13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="X13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
       <c r="Y13" t="n">
-        <v>42</v>
+        <v>46.74294587617866</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,28 +28407,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,28 +28644,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
         <v>93.35918011667277</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,28 +28881,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
         <v>93.35918011667277</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,28 +29118,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
         <v>93.35918011667277</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="C26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="D26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="E26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="G26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="I26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="S26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="T26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="U26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="V26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="W26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="X26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="Y26" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="C27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="D27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="G27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="H27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="I27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="S27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="T27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="U27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="V27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="W27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="X27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="Y27" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="C28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="D28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="E28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="F28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="G28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="H28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="J28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29400,31 +29400,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
-        <v>86.16204325169439</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="R28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="S28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="T28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="U28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="V28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="W28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="X28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
       <c r="Y28" t="n">
-        <v>87</v>
+        <v>86.16204325169437</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y29" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="30">
@@ -29513,22 +29513,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y30" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y31" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y32" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="33">
@@ -29750,22 +29750,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -29801,25 +29801,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y33" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y34" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y35" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="36">
@@ -29987,22 +29987,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y36" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y37" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y38" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="39">
@@ -30224,22 +30224,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y39" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="C40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="D40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="E40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="F40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="G40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="H40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="I40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="S40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="T40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="U40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="V40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="W40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="X40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
       <c r="Y40" t="n">
-        <v>133</v>
+        <v>132.904989127873</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y41" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="42">
@@ -30461,25 +30461,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
@@ -30509,28 +30509,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y42" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y43" t="n">
-        <v>98</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="44">
